--- a/tabular/genus/ave-refseqs-side-data.xlsx
+++ b/tabular/genus/ave-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB67D51-15E7-E34A-86C9-664846CC5F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F0357F-DE95-CB4C-8C7C-C91148AA2326}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="8080" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -2034,7 +2034,32 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2052,6 +2077,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A565BB83-608C-A244-8D08-18EA8B8CE61A}" name="Table1" displayName="Table1" ref="A1:M5" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:M5" xr:uid="{38F21FDA-CEB1-1847-A899-3EB0E8E38A79}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{44086761-72E7-A44E-A083-080CA96EE9BF}" name="sequenceID"/>
+    <tableColumn id="2" xr3:uid="{525E6C0D-6FDD-1A49-8989-3074A31966B5}" name="virus_name"/>
+    <tableColumn id="3" xr3:uid="{B4A152A7-1673-7841-9FCD-358E527DB150}" name="virus_full_name"/>
+    <tableColumn id="4" xr3:uid="{E83FA83F-C63A-574C-A712-E39090652204}" name="host_species"/>
+    <tableColumn id="5" xr3:uid="{8BC7588B-639E-0141-9E54-255A2D157040}" name="assign_clade"/>
+    <tableColumn id="6" xr3:uid="{C97F873D-5636-0645-9A6D-943551C442B1}" name="virus_genus"/>
+    <tableColumn id="7" xr3:uid="{575C3049-328C-4D41-B9B3-572A8CD5AEB7}" name="virus_subfamily"/>
+    <tableColumn id="8" xr3:uid="{E50D87DD-CBD4-CF40-A5D2-864C169D2427}" name="assign_subclade"/>
+    <tableColumn id="9" xr3:uid="{E3EEE09B-6519-2748-A7FB-C1075AAE9B96}" name="virus_clade_ns"/>
+    <tableColumn id="10" xr3:uid="{1FCB082B-E937-F943-AAA7-99105A798CB7}" name="virus_subclade_ns"/>
+    <tableColumn id="11" xr3:uid="{34792DCB-5791-D749-8F86-4B5BADFD7E99}" name="virus_clade_vp"/>
+    <tableColumn id="12" xr3:uid="{25E8D300-8368-D34D-9ADB-FDFCC4A8CF12}" name="virus_subclade_vp"/>
+    <tableColumn id="13" xr3:uid="{4AE7E4D6-2451-1042-AFA9-8CB0CD0F69EF}" name="lab_construct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2387,7 +2434,7 @@
     <col min="6" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
     <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
@@ -2603,6 +2650,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
